--- a/data/data/ICICI Prudential Mutual Fund/ICICI PRUDENTIAL HOUSING OPPORTUNITIES FUND.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI PRUDENTIAL HOUSING OPPORTUNITIES FUND.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="147">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI PRUDENTIAL HOUSING OPPORTUNITIES FUND</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,30 +61,30 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>ICICI Bank Ltd.</t>
   </si>
   <si>
     <t>INE090A01021</t>
   </si>
   <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
     <t>NTPC Ltd.</t>
   </si>
   <si>
@@ -103,37 +103,169 @@
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Orient Electric Ltd.</t>
+  </si>
+  <si>
+    <t>INE142Z01019</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
     <t>Grasim Industries Ltd.</t>
   </si>
   <si>
     <t>INE047A01021</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Kajaria Ceramics Ltd.</t>
+  </si>
+  <si>
+    <t>INE217B01036</t>
+  </si>
+  <si>
+    <t>Sobha Ltd.</t>
+  </si>
+  <si>
+    <t>INE671H01015</t>
+  </si>
+  <si>
+    <t>Birla Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE340A01012</t>
+  </si>
+  <si>
+    <t>Crompton Greaves Consumer Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE299U01018</t>
+  </si>
+  <si>
+    <t>La Opala RG Ltd.</t>
+  </si>
+  <si>
+    <t>INE059D01020</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A01026</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Bajaj Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE193E01025</t>
+  </si>
+  <si>
+    <t>The Phoenix Mills Ltd.</t>
+  </si>
+  <si>
+    <t>INE211B01039</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd</t>
+  </si>
+  <si>
+    <t>INE220B01022</t>
+  </si>
+  <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
+  </si>
+  <si>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>V-Guard Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE951I01027</t>
+  </si>
+  <si>
+    <t>Nuvoco Vistas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE118D01016</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>NLC India Ltd.</t>
+  </si>
+  <si>
+    <t>INE589A01014</t>
+  </si>
+  <si>
+    <t>RR Kabel Ltd.</t>
+  </si>
+  <si>
+    <t>INE777K01022</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>PSP Projects Ltd</t>
+  </si>
+  <si>
+    <t>INE488V01015</t>
   </si>
   <si>
     <t>Havells India Ltd.</t>
@@ -142,139 +274,10 @@
     <t>INE176B01034</t>
   </si>
   <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Orient Electric Ltd.</t>
-  </si>
-  <si>
-    <t>INE142Z01019</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Sobha Ltd.</t>
-  </si>
-  <si>
-    <t>INE671H01015</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Kajaria Ceramics Ltd.</t>
-  </si>
-  <si>
-    <t>INE217B01036</t>
-  </si>
-  <si>
-    <t>La Opala RG Ltd.</t>
-  </si>
-  <si>
-    <t>INE059D01020</t>
-  </si>
-  <si>
-    <t>Nirlon Ltd.</t>
-  </si>
-  <si>
-    <t>INE910A01012</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Nuvoco Vistas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE118D01016</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
-  </si>
-  <si>
-    <t>Bajaj Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE193E01025</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd.</t>
-  </si>
-  <si>
-    <t>INE093I01010</t>
-  </si>
-  <si>
-    <t>Crompton Greaves Consumer Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE299U01018</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd</t>
-  </si>
-  <si>
-    <t>INE220B01022</t>
-  </si>
-  <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A01026</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Birla Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE340A01012</t>
-  </si>
-  <si>
-    <t>PSP Projects Ltd</t>
-  </si>
-  <si>
-    <t>INE488V01015</t>
-  </si>
-  <si>
-    <t>The Ramco Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE331A01037</t>
-  </si>
-  <si>
-    <t>RR Kabel Ltd.</t>
-  </si>
-  <si>
-    <t>INE777K01022</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
+    <t>Somany Ceramics Ltd.</t>
+  </si>
+  <si>
+    <t>INE355A01028</t>
   </si>
   <si>
     <t>Universal Cables Ltd</t>
@@ -283,16 +286,58 @@
     <t>INE279A01012</t>
   </si>
   <si>
+    <t>Mahindra Lifespace Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE813A01018</t>
+  </si>
+  <si>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>The India Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE383A01012</t>
+  </si>
+  <si>
     <t>Prince Pipes And Fittings Ltd.</t>
   </si>
   <si>
     <t>INE689W01016</t>
   </si>
   <si>
-    <t>DLF Ltd.</t>
-  </si>
-  <si>
-    <t>INE271C01023</t>
+    <t>Greenpanel Industries Ltd</t>
+  </si>
+  <si>
+    <t>INE08ZM01014</t>
+  </si>
+  <si>
+    <t>Ttk Prestige Ltd.</t>
+  </si>
+  <si>
+    <t>INE690A01028</t>
+  </si>
+  <si>
+    <t>Whirlpool of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE716A01013</t>
+  </si>
+  <si>
+    <t>Repco Home Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE612J01015</t>
+  </si>
+  <si>
+    <t>Mahindra Lifespace Developers Ltd (Right Share)</t>
+  </si>
+  <si>
+    <t>INE813A20018</t>
   </si>
   <si>
     <t>Voltas Ltd.</t>
@@ -301,40 +346,7 @@
     <t>INE226A01021</t>
   </si>
   <si>
-    <t>V-Guard Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE951I01027</t>
-  </si>
-  <si>
-    <t>Somany Ceramics Ltd.</t>
-  </si>
-  <si>
-    <t>INE355A01028</t>
-  </si>
-  <si>
-    <t>NLC India Ltd.</t>
-  </si>
-  <si>
-    <t>INE589A01014</t>
-  </si>
-  <si>
-    <t>Repco Home Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE612J01015</t>
-  </si>
-  <si>
-    <t>Whirlpool of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE716A01013</t>
-  </si>
-  <si>
-    <t>Prestige Estates Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE811K01011</t>
+    <t>^</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -373,7 +385,7 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X417</t>
+    <t>IN002025X018</t>
   </si>
   <si>
     <t>SOV</t>
@@ -382,16 +394,16 @@
     <t>182 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z471</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
+    <t>IN002024Y407</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>IN002024Y423</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -403,18 +415,6 @@
     <t>INE041025011</t>
   </si>
   <si>
-    <t>Brookfield India Real Estate Trust REIT</t>
-  </si>
-  <si>
-    <t>INE0FDU25010</t>
-  </si>
-  <si>
-    <t>MINDSPACE BUSINESS PARKS REIT</t>
-  </si>
-  <si>
-    <t>INE0CCU25019</t>
-  </si>
-  <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
   </si>
   <si>
@@ -436,13 +436,16 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -452,19 +455,17 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Housing Index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="\^"/>
+    <numFmt numFmtId="180" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -654,7 +655,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -706,7 +707,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -715,6 +716,10 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -825,13 +830,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -849,7 +854,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="19697700"/>
+          <a:off x="666750" y="20078700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -864,13 +869,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -888,7 +893,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="22555200"/>
+          <a:off x="666750" y="22936200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1222,19 +1227,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J115"/>
+  <dimension ref="B1:J116"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="47.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="47.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1322,10 +1327,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>208273.00999999998</v>
+        <v>216378.54999999993</v>
       </c>
       <c r="H5" s="10">
-        <v>0.8733459464613001</v>
+        <v>0.8821594594164</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1359,10 +1364,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>208273.00999999998</v>
+        <v>216378.54999999993</v>
       </c>
       <c r="H7" s="10">
-        <v>0.8733459464613001</v>
+        <v>0.8821594594164</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1385,13 +1390,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>1772327</v>
+        <v>666461</v>
       </c>
       <c r="G8" s="15">
-        <v>22203.71</v>
+        <v>24493.11</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0931062557022</v>
+        <v>0.099856610912</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1414,13 +1419,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>602023</v>
+        <v>1108250</v>
       </c>
       <c r="G9" s="15">
-        <v>21476.57</v>
+        <v>21554.35</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0900571579266</v>
+        <v>0.0878755021887</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1440,16 +1445,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" s="14">
-        <v>1055169</v>
+        <v>1447450</v>
       </c>
       <c r="G10" s="15">
-        <v>17924.68</v>
+        <v>20927.23</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0751631074024</v>
+        <v>0.0853187799988</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1472,13 +1477,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>5050712</v>
+        <v>5867006</v>
       </c>
       <c r="G11" s="15">
-        <v>16364.31</v>
+        <v>19589.93</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0686200473367</v>
+        <v>0.0798667060983</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1501,13 +1506,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>97583</v>
+        <v>115755</v>
       </c>
       <c r="G12" s="15">
-        <v>11209.80</v>
+        <v>12976.14</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0470057708901</v>
+        <v>0.0529027699267</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1527,16 +1532,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F13" s="14">
-        <v>441599</v>
+        <v>1158288</v>
       </c>
       <c r="G13" s="15">
-        <v>11079.06</v>
+        <v>9408.77</v>
       </c>
       <c r="H13" s="16">
-        <v>0.046457542154</v>
+        <v>0.0383588643929</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1556,16 +1561,16 @@
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F14" s="14">
-        <v>1058406</v>
+        <v>1504674</v>
       </c>
       <c r="G14" s="15">
-        <v>10436.94</v>
+        <v>8328.37</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0437649565946</v>
+        <v>0.0339541529279</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1588,13 +1593,13 @@
         <v>35</v>
       </c>
       <c r="F15" s="14">
-        <v>5609571</v>
+        <v>5001373</v>
       </c>
       <c r="G15" s="15">
-        <v>7551.60</v>
+        <v>8053.21</v>
       </c>
       <c r="H15" s="16">
-        <v>0.031665933331</v>
+        <v>0.0328323458133</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1614,16 +1619,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>1461182</v>
+        <v>611203</v>
       </c>
       <c r="G16" s="15">
-        <v>7492.94</v>
+        <v>7286.76</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0314199558362</v>
+        <v>0.0297075854446</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1643,16 +1648,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>910212</v>
+        <v>2948175</v>
       </c>
       <c r="G17" s="15">
-        <v>7035.03</v>
+        <v>6689.11</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0294998134119</v>
+        <v>0.0272710102807</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1663,25 +1668,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F18" s="14">
-        <v>392346</v>
+        <v>215244</v>
       </c>
       <c r="G18" s="15">
-        <v>6144.92</v>
+        <v>5479.68</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0257673376561</v>
+        <v>0.0223402529806</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1701,16 +1706,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F19" s="14">
-        <v>2551569</v>
+        <v>308913</v>
       </c>
       <c r="G19" s="15">
-        <v>5604.52</v>
+        <v>5394.55</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0235012920006</v>
+        <v>0.0219931842218</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1721,25 +1726,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>18968</v>
+        <v>455630</v>
       </c>
       <c r="G20" s="15">
-        <v>5272.33</v>
+        <v>4737.41</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0221083280734</v>
+        <v>0.0193140726964</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1750,25 +1755,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F21" s="14">
-        <v>183186</v>
+        <v>324844</v>
       </c>
       <c r="G21" s="15">
-        <v>4214.74</v>
+        <v>4655.01</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0176735626685</v>
+        <v>0.0189781339471</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1779,25 +1784,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F22" s="14">
-        <v>310017</v>
+        <v>316844</v>
       </c>
       <c r="G22" s="15">
-        <v>4110.21</v>
+        <v>4354.70</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0172352396626</v>
+        <v>0.0177537921292</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1817,16 +1822,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F23" s="14">
-        <v>381502</v>
+        <v>1081268</v>
       </c>
       <c r="G23" s="15">
-        <v>3782.21</v>
+        <v>3815.79</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0158598455564</v>
+        <v>0.015556695632</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1846,16 +1851,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F24" s="14">
-        <v>1208911</v>
+        <v>1380968</v>
       </c>
       <c r="G24" s="15">
-        <v>3276.75</v>
+        <v>3396.49</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0137403129194</v>
+        <v>0.0138472403217</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1878,13 +1883,13 @@
         <v>58</v>
       </c>
       <c r="F25" s="14">
-        <v>630100</v>
+        <v>558120</v>
       </c>
       <c r="G25" s="15">
-        <v>3193.66</v>
+        <v>3328.91</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0133918937234</v>
+        <v>0.0135717216242</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1904,16 +1909,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
-        <v>905377</v>
+        <v>460608</v>
       </c>
       <c r="G26" s="15">
-        <v>3173.35</v>
+        <v>3163</v>
       </c>
       <c r="H26" s="16">
-        <v>0.013306728314</v>
+        <v>0.0128953187371</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1933,16 +1938,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F27" s="14">
-        <v>154825</v>
+        <v>201401</v>
       </c>
       <c r="G27" s="15">
-        <v>3108.34</v>
+        <v>3095.73</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0130341235248</v>
+        <v>0.0126210638869</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1962,16 +1967,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F28" s="14">
-        <v>423304</v>
+        <v>259055</v>
       </c>
       <c r="G28" s="15">
-        <v>2965.67</v>
+        <v>2949.99</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0124358690213</v>
+        <v>0.0120268926087</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1991,16 +1996,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F29" s="14">
-        <v>286558</v>
+        <v>154825</v>
       </c>
       <c r="G29" s="15">
-        <v>2840.36</v>
+        <v>2915.05</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0119104097669</v>
+        <v>0.0118844447944</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2020,16 +2025,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F30" s="14">
-        <v>143768</v>
+        <v>192234</v>
       </c>
       <c r="G30" s="15">
-        <v>2606.01</v>
+        <v>2819.30</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0109277158377</v>
+        <v>0.0114940790754</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2049,16 +2054,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F31" s="14">
-        <v>743495</v>
+        <v>680402</v>
       </c>
       <c r="G31" s="15">
-        <v>2553.16</v>
+        <v>2581.10</v>
       </c>
       <c r="H31" s="16">
-        <v>0.010706101269</v>
+        <v>0.0105229551667</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2078,16 +2083,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F32" s="14">
-        <v>228173</v>
+        <v>686764</v>
       </c>
       <c r="G32" s="15">
-        <v>2415.55</v>
+        <v>2457.58</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0101290647356</v>
+        <v>0.010019373197</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2107,16 +2112,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F33" s="14">
-        <v>128659</v>
+        <v>286558</v>
       </c>
       <c r="G33" s="15">
-        <v>2401.23</v>
+        <v>2341.04</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0100690170417</v>
+        <v>0.0095442481746</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2136,16 +2141,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F34" s="14">
-        <v>398909</v>
+        <v>96186</v>
       </c>
       <c r="G34" s="15">
-        <v>2385.87</v>
+        <v>2172.94</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0100046083421</v>
+        <v>0.0088589168184</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2156,25 +2161,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F35" s="14">
-        <v>195527</v>
+        <v>840849</v>
       </c>
       <c r="G35" s="15">
-        <v>2282.78</v>
+        <v>2032.50</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0095723236518</v>
+        <v>0.0082863532511</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2185,25 +2190,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="F36" s="14">
-        <v>282327</v>
+        <v>128285</v>
       </c>
       <c r="G36" s="15">
-        <v>1788.54</v>
+        <v>1828.96</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0074998395571</v>
+        <v>0.0074565356173</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2223,16 +2228,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F37" s="14">
-        <v>175295</v>
+        <v>282327</v>
       </c>
       <c r="G37" s="15">
-        <v>1608.33</v>
+        <v>1804.21</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0067441695209</v>
+        <v>0.0073556316847</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2252,16 +2257,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F38" s="14">
-        <v>111961</v>
+        <v>110484</v>
       </c>
       <c r="G38" s="15">
-        <v>1372.64</v>
+        <v>1687.09</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0057558566035</v>
+        <v>0.0068781420449</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2272,25 +2277,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F39" s="14">
-        <v>213970</v>
+        <v>349713</v>
       </c>
       <c r="G39" s="15">
-        <v>1364.38</v>
+        <v>1672.68</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0057212201544</v>
+        <v>0.0068193935331</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2301,25 +2306,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>90</v>
-      </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F40" s="14">
-        <v>332868</v>
+        <v>278325</v>
       </c>
       <c r="G40" s="15">
-        <v>1233.61</v>
+        <v>1662.02</v>
       </c>
       <c r="H40" s="16">
-        <v>0.00517286562</v>
+        <v>0.0067759334959</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2330,25 +2335,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>92</v>
-      </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F41" s="14">
-        <v>160235</v>
+        <v>390311</v>
       </c>
       <c r="G41" s="15">
-        <v>1193.83</v>
+        <v>1353.99</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0050060571519</v>
+        <v>0.0055201178049</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2359,25 +2364,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>94</v>
-      </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F42" s="14">
-        <v>80231</v>
+        <v>327724</v>
       </c>
       <c r="G42" s="15">
-        <v>1011.59</v>
+        <v>1287.30</v>
       </c>
       <c r="H42" s="16">
-        <v>0.004241874768</v>
+        <v>0.005248227572</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2388,25 +2393,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F43" s="14">
-        <v>239209</v>
+        <v>357792</v>
       </c>
       <c r="G43" s="15">
-        <v>871.80</v>
+        <v>1134.74</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0036556968957</v>
+        <v>0.0046262516547</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2417,25 +2422,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="F44" s="14">
-        <v>165704</v>
+        <v>332868</v>
       </c>
       <c r="G44" s="15">
-        <v>845.09</v>
+        <v>1114.61</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0035436945281</v>
+        <v>0.0045441831228</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2446,25 +2451,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>100</v>
-      </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F45" s="14">
-        <v>261880</v>
+        <v>202239</v>
       </c>
       <c r="G45" s="15">
-        <v>581.16</v>
+        <v>515.99</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0024369635328</v>
+        <v>0.0021036533402</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2475,25 +2480,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F46" s="14">
-        <v>144695</v>
+        <v>80167</v>
       </c>
       <c r="G46" s="15">
-        <v>568.94</v>
+        <v>498.52</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0023857217158</v>
+        <v>0.002032429433</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2504,25 +2509,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>104</v>
-      </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F47" s="14">
         <v>38306</v>
       </c>
       <c r="G47" s="15">
-        <v>436.61</v>
+        <v>473.42</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0018308256729</v>
+        <v>0.0019300985762</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2533,25 +2538,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>106</v>
-      </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F48" s="14">
-        <v>21345</v>
+        <v>54825</v>
       </c>
       <c r="G48" s="15">
-        <v>290.19</v>
+        <v>214.06</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0012168463892</v>
+        <v>0.0008727069013</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2562,6 +2567,27 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" s="14">
+        <v>146366</v>
+      </c>
+      <c r="G49" s="15">
+        <v>131.58</v>
+      </c>
+      <c r="H49" s="16">
+        <v>0.0005364419979</v>
+      </c>
+      <c r="I49" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -2569,28 +2595,28 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
+      <c r="B50" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="H50" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I50" s="9" t="s">
+      <c r="C50" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" s="14">
+        <v>129</v>
+      </c>
+      <c r="G50" s="15">
+        <v>1.63</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I50" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -2607,7 +2633,7 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>13</v>
@@ -2622,10 +2648,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>13</v>
@@ -2644,7 +2670,7 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>13</v>
@@ -2659,10 +2685,10 @@
         <v>13</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>13</v>
@@ -2681,7 +2707,7 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="7" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>13</v>
@@ -2696,10 +2722,10 @@
         <v>13</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>13</v>
@@ -2718,7 +2744,7 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>13</v>
@@ -2733,10 +2759,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I58" s="9" t="s">
         <v>13</v>
@@ -2755,25 +2781,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="H60" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>13</v>
@@ -2792,7 +2818,7 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>13</v>
@@ -2807,10 +2833,10 @@
         <v>13</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>13</v>
@@ -2829,7 +2855,7 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>13</v>
@@ -2843,11 +2869,11 @@
       <c r="F64" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="9">
-        <v>1886.86</v>
-      </c>
-      <c r="H64" s="10">
-        <v>0.0079121223268</v>
+      <c r="G64" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="I64" s="9" t="s">
         <v>13</v>
@@ -2866,7 +2892,7 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>13</v>
@@ -2880,11 +2906,11 @@
       <c r="F66" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>108</v>
+      <c r="G66" s="9">
+        <v>4968.99</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0.020258207351</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>13</v>
@@ -2903,7 +2929,7 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>13</v>
@@ -2918,10 +2944,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>13</v>
@@ -2940,7 +2966,7 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>13</v>
@@ -2954,11 +2980,11 @@
       <c r="F70" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="9">
-        <v>1886.86</v>
-      </c>
-      <c r="H70" s="10">
-        <v>0.0079121223268</v>
+      <c r="G70" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="I70" s="9" t="s">
         <v>13</v>
@@ -2969,57 +2995,36 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F71" s="14">
-        <v>600000</v>
-      </c>
-      <c r="G71" s="15">
-        <v>592.07</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0024827121599</v>
-      </c>
-      <c r="I71" s="15">
-        <v>6.52</v>
+        <v>13</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F72" s="14">
-        <v>500000</v>
-      </c>
-      <c r="G72" s="15">
-        <v>499.56</v>
-      </c>
-      <c r="H72" s="16">
-        <v>0.0020947923161</v>
-      </c>
-      <c r="I72" s="15">
-        <v>6.37</v>
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9">
+        <v>4968.99</v>
+      </c>
+      <c r="H72" s="10">
+        <v>0.020258207351</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3027,28 +3032,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="D73" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D73" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>120</v>
-      </c>
       <c r="F73" s="14">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="G73" s="15">
-        <v>499.56</v>
+        <v>1990.19</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0020947923161</v>
+        <v>0.008113858488</v>
       </c>
       <c r="I73" s="15">
-        <v>6.37</v>
+        <v>5.62</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3056,28 +3061,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F74" s="14">
-        <v>300000</v>
+        <v>1350000</v>
       </c>
       <c r="G74" s="15">
-        <v>295.67</v>
+        <v>1340.52</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0012398255347</v>
+        <v>0.005465201604</v>
       </c>
       <c r="I74" s="15">
-        <v>6.51</v>
+        <v>5.61</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3085,36 +3090,57 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>13</v>
+        <v>122</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" s="14">
+        <v>1000000</v>
+      </c>
+      <c r="G75" s="15">
+        <v>993.90</v>
+      </c>
+      <c r="H75" s="16">
+        <v>0.0040520573167</v>
+      </c>
+      <c r="I75" s="15">
+        <v>5.60</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="9">
-        <v>10676.48</v>
-      </c>
-      <c r="H76" s="10">
-        <v>0.044769413619400004</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>13</v>
+      <c r="B76" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F76" s="14">
+        <v>500000</v>
+      </c>
+      <c r="G76" s="15">
+        <v>495.43</v>
+      </c>
+      <c r="H76" s="16">
+        <v>0.0020198317299</v>
+      </c>
+      <c r="I76" s="15">
+        <v>5.61</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3122,28 +3148,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F77" s="14">
-        <v>1585032</v>
+        <v>150000</v>
       </c>
       <c r="G77" s="15">
-        <v>5866.84</v>
+        <v>148.95</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0246012718236</v>
-      </c>
-      <c r="I77" s="15" t="s">
-        <v>13</v>
+        <v>0.0006072582124</v>
+      </c>
+      <c r="I77" s="15">
+        <v>5.61</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3151,56 +3177,35 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C78" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D78" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="F78" s="14">
-        <v>857889</v>
-      </c>
-      <c r="G78" s="15">
-        <v>2557.62</v>
-      </c>
-      <c r="H78" s="16">
-        <v>0.0107248032742</v>
-      </c>
-      <c r="I78" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="F79" s="14">
-        <v>602144</v>
-      </c>
-      <c r="G79" s="15">
-        <v>2252.02</v>
-      </c>
-      <c r="H79" s="16">
-        <v>0.0094433385216</v>
-      </c>
-      <c r="I79" s="15" t="s">
+      <c r="C79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="9">
+        <v>4432.17</v>
+      </c>
+      <c r="H79" s="10">
+        <v>0.0180696316305</v>
+      </c>
+      <c r="I79" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J79" s="11" t="s">
@@ -3209,6 +3214,27 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F80" s="14">
+        <v>1162080</v>
+      </c>
+      <c r="G80" s="15">
+        <v>4432.17</v>
+      </c>
+      <c r="H80" s="16">
+        <v>0.0180696316305</v>
+      </c>
+      <c r="I80" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J80" s="11" t="s">
@@ -3216,36 +3242,36 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J82" s="11" t="s">
@@ -3253,36 +3279,36 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9">
-        <v>16475.57</v>
-      </c>
-      <c r="H83" s="10">
-        <v>0.0690865910813</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9">
+        <v>19289.85</v>
+      </c>
+      <c r="H84" s="10">
+        <v>0.0786433019736</v>
+      </c>
+      <c r="I84" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J84" s="11" t="s">
@@ -3290,50 +3316,36 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9">
-        <v>311.50</v>
-      </c>
-      <c r="H85" s="10">
-        <v>0.0013062050734</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="13"/>
-      <c r="G86" s="15">
-        <v>311.50</v>
-      </c>
-      <c r="H86" s="16">
-        <v>0.0013062050734</v>
-      </c>
-      <c r="I86" s="15" t="s">
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9">
+        <v>711.50</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0.0029007332537</v>
+      </c>
+      <c r="I86" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J86" s="11" t="s">
@@ -3342,6 +3354,20 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="13"/>
+      <c r="G87" s="15">
+        <v>711.50</v>
+      </c>
+      <c r="H87" s="16">
+        <v>0.0029007332537</v>
+      </c>
+      <c r="I87" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J87" s="11" t="s">
@@ -3349,144 +3375,159 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="17" t="s">
+      <c r="B88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C88" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="18">
-        <v>853.6815923500399</v>
-      </c>
-      <c r="H88" s="19">
-        <v>0.003579721435097418</v>
-      </c>
-      <c r="I88" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="17" t="s">
+      <c r="C89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="19">
+        <v>-498.25121769987163</v>
+      </c>
+      <c r="H89" s="20">
+        <v>-0.0020313336273888355</v>
+      </c>
+      <c r="I89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C89" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="18">
-        <v>238477.10159235</v>
-      </c>
-      <c r="H89" s="19">
-        <v>0.9999999999972976</v>
-      </c>
-      <c r="I89" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" ht="15" customHeight="1">
-      <c r="B92" s="13" t="s">
+      <c r="C90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="19">
+        <v>245282.8087823</v>
+      </c>
+      <c r="H90" s="20">
+        <v>0.9999999999978114</v>
+      </c>
+      <c r="I90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="15" customHeight="1">
+      <c r="B93" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C92" s="21"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
-      <c r="G92" s="21"/>
-      <c r="H92" s="21"/>
-      <c r="I92" s="21"/>
-    </row>
-    <row r="93" spans="2:8" ht="15" customHeight="1">
-      <c r="B93" s="13" t="s">
+      <c r="C93" s="22"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="22"/>
+    </row>
+    <row r="94" spans="2:8" ht="15" customHeight="1">
+      <c r="B94" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C93" s="21"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21"/>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21"/>
-    </row>
-    <row r="94" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B94" s="22" t="s">
+      <c r="C94" s="22"/>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+    </row>
+    <row r="95" spans="2:8" ht="15" customHeight="1">
+      <c r="B95" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C94" s="21"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
-    </row>
-    <row r="95" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B95" s="22" t="s">
+      <c r="C95" s="22"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="22"/>
+      <c r="H95" s="22"/>
+    </row>
+    <row r="96" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B96" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C95" s="21"/>
-      <c r="D95" s="21"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="21"/>
-      <c r="G95" s="21"/>
-      <c r="H95" s="21"/>
-    </row>
-    <row r="96" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B96" s="22" t="s">
+      <c r="C96" s="22"/>
+      <c r="D96" s="22"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="22"/>
+    </row>
+    <row r="97" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B97" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C96" s="21"/>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="21"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="21"/>
-    </row>
-    <row r="99" ht="15">
-      <c r="B99" s="21" t="s">
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+    </row>
+    <row r="98" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B98" s="23" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="114" ht="15">
-      <c r="B114" s="21" t="s">
+      <c r="C98" s="22"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+    </row>
+    <row r="101" ht="15">
+      <c r="B101" s="22" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="115" ht="15">
-      <c r="B115" s="21" t="s">
+    <row r="116" ht="15">
+      <c r="B116" s="22" t="s">
         <v>146</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B94:H94"/>
+  <mergeCells count="9">
     <mergeCell ref="B95:H95"/>
     <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B98:H98"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B92:I92"/>
-    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:H94"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
